--- a/assets/starter-pack/rebuilt/FLK_01_SAM_PreReg_Checklist.xlsx
+++ b/assets/starter-pack/rebuilt/FLK_01_SAM_PreReg_Checklist.xlsx
@@ -4,28 +4,58 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Dashboard" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Checklist" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Quick Reference" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Timeline" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Instructions" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Dashboard" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Checklist" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Quick Reference" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Timeline" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Instructions" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="StatusOptions">Lists!$A$2:$A$4</definedName>
+    <definedName name="RequiredOptions">Lists!$B$2:$B$5</definedName>
     <definedName name="StatusRange">Checklist!$E$6:$E$45</definedName>
     <definedName name="RequiredRange">Checklist!$D$6:$D$45</definedName>
     <definedName name="KickoffDate">Timeline!$C$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Quick Reference'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Timeline'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Instructions'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Dashboard'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Checklist'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Quick Reference'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Timeline'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Instructions'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="247">
+  <si>
+    <t>My Status</t>
+  </si>
+  <si>
+    <t>Required?</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Need to get</t>
+  </si>
+  <si>
+    <t>Recommended</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>If applicable</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
   <si>
     <t>CAPTUREPILOT  ·  SAM Pre-Reg Dashboard</t>
   </si>
@@ -63,9 +93,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>Remaining</t>
   </si>
   <si>
@@ -117,12 +144,6 @@
     <t>Where to Find It · Notes</t>
   </si>
   <si>
-    <t>Required?</t>
-  </si>
-  <si>
-    <t>My Status</t>
-  </si>
-  <si>
     <t>Owner / Due Date</t>
   </si>
   <si>
@@ -135,9 +156,6 @@
     <t>Pull from IRS Letter CP 575 or 147C. Copy character-for-character including commas, periods, spacing.</t>
   </si>
   <si>
-    <t>Required</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -225,9 +243,6 @@
     <t>Add every relevant code. Agencies filter by NAICS when searching vendors. More codes mean more visibility.</t>
   </si>
   <si>
-    <t>Recommended</t>
-  </si>
-  <si>
     <t xml:space="preserve">  SECTION 4 — Banking &amp; Payment (EFT)</t>
   </si>
   <si>
@@ -262,9 +277,6 @@
   </si>
   <si>
     <t>Only if you already have active 8(a) status. Apply at certify.sba.gov after SAM activation if you qualify.</t>
-  </si>
-  <si>
-    <t>If applicable</t>
   </si>
   <si>
     <t>HUBZone certification letter (SBA-issued)</t>
@@ -766,12 +778,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -852,11 +873,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF111827"/>
       <sz val="10"/>
       <name val="Calibri"/>
@@ -890,12 +906,17 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -975,48 +996,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1028,98 +1055,98 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1580,6 +1607,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1593,266 +1671,266 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="11">
+        <f>COUNTA(Checklist!D6:D45)</f>
+      </c>
+      <c r="C7" s="11">
+        <f>COUNTIF(Checklist!E6:E45,"Done")</f>
+      </c>
+      <c r="D7" s="11">
+        <f>COUNTIF(Checklist!E6:E45,"Need to get")</f>
+      </c>
+      <c r="E7" s="11">
+        <f>COUNTIF(Checklist!E6:E45,"N/A")</f>
+      </c>
+      <c r="F7" s="12">
+        <f>IFERROR(COUNTIF(Checklist!E6:E45,"Done")/COUNTA(Checklist!D6:D45),0)</f>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="14">
+        <f>IFERROR(COUNTIFS(Checklist!D6:D45,"Required",Checklist!E6:E45,"Done")/COUNTIF(Checklist!D6:D45,"Required"),0)</f>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
-        <f>COUNTA(Checklist!D6:D45)</f>
-      </c>
-      <c r="C7" s="9">
-        <f>COUNTIF(Checklist!E6:E45,"Done")</f>
-      </c>
-      <c r="D7" s="9">
-        <f>COUNTIF(Checklist!E6:E45,"Need to get")</f>
-      </c>
-      <c r="E7" s="9">
-        <f>COUNTIF(Checklist!E6:E45,"N/A")</f>
-      </c>
-      <c r="F7" s="10">
-        <f>IFERROR(COUNTIF(Checklist!E6:E45,"Done")/COUNTA(Checklist!D6:D45),0)</f>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" ht="40" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="12">
-        <f>IFERROR(COUNTIFS(Checklist!D6:D45,"Required",Checklist!E6:E45,"Done")/COUNTIF(Checklist!D6:D45,"Required"),0)</f>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>14</v>
+      <c r="E14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="16">
+      <c r="B15" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="18">
         <f>COUNTA(Checklist!D6:D12)</f>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="18">
         <f>COUNTIF(Checklist!E6:E12,"Done")</f>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="18">
         <f>COUNTIF(Checklist!E6:E12,"Need to get")</f>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>IFERROR(COUNTIF(Checklist!E6:E12,"Done")/COUNTA(Checklist!D6:D12),0)</f>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="19">
+      <c r="B16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="21">
         <f>COUNTA(Checklist!D14:D17)</f>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="21">
         <f>COUNTIF(Checklist!E14:E17,"Done")</f>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="21">
         <f>COUNTIF(Checklist!E14:E17,"Need to get")</f>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="22">
         <f>IFERROR(COUNTIF(Checklist!E14:E17,"Done")/COUNTA(Checklist!D14:D17),0)</f>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="16">
+      <c r="B17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="18">
         <f>COUNTA(Checklist!D19:D21)</f>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="18">
         <f>COUNTIF(Checklist!E19:E21,"Done")</f>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="18">
         <f>COUNTIF(Checklist!E19:E21,"Need to get")</f>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="19">
         <f>IFERROR(COUNTIF(Checklist!E19:E21,"Done")/COUNTA(Checklist!D19:D21),0)</f>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="19">
+      <c r="B18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="21">
         <f>COUNTA(Checklist!D23:D26)</f>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="21">
         <f>COUNTIF(Checklist!E23:E26,"Done")</f>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="21">
         <f>COUNTIF(Checklist!E23:E26,"Need to get")</f>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="22">
         <f>IFERROR(COUNTIF(Checklist!E23:E26,"Done")/COUNTA(Checklist!D23:D26),0)</f>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="16">
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="18">
         <f>COUNTA(Checklist!D28:D31)</f>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="18">
         <f>COUNTIF(Checklist!E28:E31,"Done")</f>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="18">
         <f>COUNTIF(Checklist!E28:E31,"Need to get")</f>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="19">
         <f>IFERROR(COUNTIF(Checklist!E28:E31,"Done")/COUNTA(Checklist!D28:D31),0)</f>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="19">
+      <c r="B20" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="21">
         <f>COUNTA(Checklist!D33:D36)</f>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="21">
         <f>COUNTIF(Checklist!E33:E36,"Done")</f>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="21">
         <f>COUNTIF(Checklist!E33:E36,"Need to get")</f>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="22">
         <f>IFERROR(COUNTIF(Checklist!E33:E36,"Done")/COUNTA(Checklist!D33:D36),0)</f>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="16">
+      <c r="B21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="18">
         <f>COUNTA(Checklist!D38:D41)</f>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="18">
         <f>COUNTIF(Checklist!E38:E41,"Done")</f>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="18">
         <f>COUNTIF(Checklist!E38:E41,"Need to get")</f>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>IFERROR(COUNTIF(Checklist!E38:E41,"Done")/COUNTA(Checklist!D38:D41),0)</f>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="19">
+      <c r="B22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="21">
         <f>COUNTA(Checklist!D43:D45)</f>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="21">
         <f>COUNTIF(Checklist!E43:E45,"Done")</f>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="21">
         <f>COUNTIF(Checklist!E43:E45,"Need to get")</f>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="22">
         <f>IFERROR(COUNTIF(Checklist!E43:E45,"Done")/COUNTA(Checklist!D43:D45),0)</f>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="B24" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="21">
+      <c r="B25" s="23">
         <f>IF(COUNTIFS(Checklist!D6:D45,"Required",Checklist!E6:E45,"Done")=COUNTIF(Checklist!D6:D45,"Required"),"READY — open sam.gov and start your registration",IF(COUNTIFS(Checklist!D6:D45,"Required",Checklist!E6:E45,"Done")/COUNTIF(Checklist!D6:D45,"Required")&gt;=0.7,"ALMOST THERE — finish the last few required items first","NOT YET — keep collecting documents. Do not start SAM.gov until required items are Done."))</f>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1896,7 +1974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0B2A4A"/>
@@ -1913,804 +1991,804 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>1</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>2</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>3</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="31">
+        <v>4</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>5</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="31">
+        <v>6</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>7</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="31">
+        <v>8</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="26">
+        <v>9</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="31">
+        <v>10</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="26">
+        <v>11</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="31">
+        <v>12</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="26">
+        <v>13</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="31">
+        <v>14</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>15</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="31">
+        <v>16</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>17</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="31">
+        <v>18</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="26">
+        <v>19</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="31">
+        <v>20</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="26">
+        <v>21</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="31">
+        <v>22</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="26">
+        <v>23</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="31">
         <v>24</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B35" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="26">
         <v>25</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="B36" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="31">
         <v>26</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="B37" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="26">
         <v>27</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B39" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="31">
         <v>28</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="B40" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="26">
         <v>29</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="B41" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="31">
         <v>30</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="B42" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+    </row>
+    <row r="44" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="26">
         <v>31</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="B44" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="31">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="B45" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="26">
         <v>33</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
-        <v>1</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
-        <v>2</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
-        <v>3</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
-        <v>4</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
-        <v>5</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
-        <v>6</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
+      <c r="B46" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="29">
-        <v>8</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="24">
-        <v>9</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="29">
-        <v>10</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="24">
-        <v>11</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
-        <v>12</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="24">
-        <v>13</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="29">
-        <v>14</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="24">
-        <v>15</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="29">
-        <v>16</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="24">
-        <v>17</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="29">
-        <v>18</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="24">
-        <v>19</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="29">
-        <v>20</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="24">
-        <v>21</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="29">
-        <v>22</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="24">
-        <v>23</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
-        <v>24</v>
-      </c>
-      <c r="B35" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="24">
-        <v>25</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="29">
-        <v>26</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="24">
-        <v>27</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
-        <v>28</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="24">
-        <v>29</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="29">
-        <v>30</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-    </row>
-    <row r="44" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="24">
-        <v>31</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="45" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="29">
-        <v>32</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E45" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F45" s="33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="24">
-        <v>33</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>37</v>
+      <c r="E46" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
+      <c r="A48" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2751,10 +2829,10 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D6:D45">
-      <formula1>"Required,Recommended,If applicable,Optional"</formula1>
+      <formula1>RequiredOptions</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use Done, Need to get, or N/A." sqref="E6:E45">
-      <formula1>"Done,Need to get,N/A"</formula1>
+      <formula1>StatusOptions</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -2765,7 +2843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFF59E0B"/>
@@ -2781,247 +2859,247 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="A5" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>116</v>
+      <c r="B6" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>118</v>
+      <c r="B7" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>120</v>
+      <c r="B8" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>122</v>
+      <c r="B9" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>124</v>
+      <c r="B10" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>126</v>
+      <c r="B11" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>128</v>
+      <c r="B12" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>130</v>
+      <c r="B13" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>132</v>
+      <c r="B14" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>134</v>
+      <c r="B15" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+      <c r="A16" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>137</v>
+      <c r="B17" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>139</v>
+      <c r="B18" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>141</v>
+      <c r="B19" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>143</v>
+      <c r="B20" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>145</v>
+      <c r="B21" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>147</v>
+      <c r="B22" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>149</v>
+      <c r="B23" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>151</v>
+      <c r="B24" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>153</v>
+      <c r="B25" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>155</v>
+      <c r="B26" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
+      <c r="A27" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>158</v>
+      <c r="B28" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>160</v>
+      <c r="B29" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>162</v>
+      <c r="B30" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>164</v>
+      <c r="B31" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>166</v>
+      <c r="B32" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3040,7 +3118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFDC2626"/>
@@ -3057,320 +3135,320 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="B4" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46178.89358017361</v>
+      <c r="B5" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="41">
+        <v>46182.99240853009</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="A6" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>175</v>
       </c>
+      <c r="D6" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
+      <c r="A7" s="26">
         <v>1</v>
       </c>
-      <c r="B7" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="42">
+      <c r="B7" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="44">
         <f>WORKDAY(KickoffDate, -7)</f>
       </c>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>2</v>
+      </c>
+      <c r="B8" s="46" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
-        <v>2</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="46">
+      <c r="C8" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="48">
         <f>WORKDAY(KickoffDate, -5)</f>
       </c>
-      <c r="F8" s="47" t="s">
-        <v>182</v>
+      <c r="F8" s="49" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
+      <c r="A9" s="26">
         <v>3</v>
       </c>
-      <c r="B9" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="E9" s="42">
+      <c r="B9" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="44">
         <f>WORKDAY(KickoffDate, -3)</f>
       </c>
-      <c r="F9" s="43" t="s">
-        <v>185</v>
+      <c r="F9" s="45" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
+      <c r="A10" s="31">
         <v>4</v>
       </c>
-      <c r="B10" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="36" t="s">
+      <c r="B10" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="48">
+        <f>WORKDAY(KickoffDate, 0)</f>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>5</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E11" s="44">
+        <f>WORKDAY(KickoffDate, 0)</f>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="31">
+        <v>6</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12" s="48">
+        <f>WORKDAY(KickoffDate, 1)</f>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>7</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="46">
-        <f>WORKDAY(KickoffDate, 0)</f>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
-        <v>5</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="42">
-        <f>WORKDAY(KickoffDate, 0)</f>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
-        <v>6</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" s="46">
+      <c r="E13" s="44">
         <f>WORKDAY(KickoffDate, 1)</f>
       </c>
-      <c r="F12" s="47" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
-        <v>7</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="42">
-        <f>WORKDAY(KickoffDate, 1)</f>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>197</v>
+      <c r="F13" s="45" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="29">
+      <c r="A14" s="31">
         <v>8</v>
       </c>
-      <c r="B14" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="46">
+      <c r="B14" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="48">
         <f>WORKDAY(KickoffDate, 2)</f>
       </c>
-      <c r="F14" s="47" t="s">
-        <v>201</v>
+      <c r="F14" s="49" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24">
+      <c r="A15" s="26">
         <v>9</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="42">
+      <c r="B15" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="44">
         <f>WORKDAY(KickoffDate, 5)</f>
       </c>
-      <c r="F15" s="43" t="s">
-        <v>205</v>
+      <c r="F15" s="45" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
+      <c r="A16" s="31">
         <v>10</v>
       </c>
-      <c r="B16" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="46">
+      <c r="B16" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="48">
         <f>WORKDAY(KickoffDate, 7)</f>
       </c>
-      <c r="F16" s="47" t="s">
-        <v>209</v>
+      <c r="F16" s="49" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="24">
+      <c r="A17" s="26">
         <v>11</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="E17" s="42">
+      <c r="B17" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" s="44">
         <f>WORKDAY(KickoffDate, 11)</f>
       </c>
-      <c r="F17" s="43" t="s">
-        <v>213</v>
+      <c r="F17" s="45" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="29">
+      <c r="A18" s="31">
         <v>12</v>
       </c>
-      <c r="B18" s="44" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="46">
+      <c r="B18" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="48">
         <f>WORKDAY(KickoffDate, 14)</f>
       </c>
-      <c r="F18" s="47" t="s">
-        <v>217</v>
+      <c r="F18" s="49" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="24">
+      <c r="A19" s="26">
         <v>13</v>
       </c>
-      <c r="B19" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="42">
+      <c r="B19" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="44">
         <f>WORKDAY(KickoffDate, 15)</f>
       </c>
-      <c r="F19" s="43" t="s">
-        <v>221</v>
+      <c r="F19" s="45" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3395,7 +3473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
@@ -3409,129 +3487,129 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="48"/>
+      <c r="A5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="50"/>
     </row>
     <row r="6" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="49" t="s">
-        <v>225</v>
+      <c r="B6" s="51" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="48"/>
+      <c r="A7" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="50"/>
     </row>
     <row r="8" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="49" t="s">
-        <v>227</v>
+      <c r="B8" s="51" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="49" t="s">
-        <v>228</v>
+      <c r="B9" s="51" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="49" t="s">
-        <v>229</v>
+      <c r="B10" s="51" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="49" t="s">
-        <v>230</v>
+      <c r="B11" s="51" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="49" t="s">
-        <v>231</v>
+      <c r="B12" s="51" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="48"/>
+      <c r="A13" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="50"/>
     </row>
     <row r="14" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="49" t="s">
-        <v>233</v>
+      <c r="B14" s="51" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="49" t="s">
-        <v>234</v>
+      <c r="B15" s="51" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="49" t="s">
-        <v>235</v>
+      <c r="B16" s="51" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="49" t="s">
-        <v>236</v>
+      <c r="B17" s="51" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>237</v>
-      </c>
-      <c r="B18" s="48"/>
+      <c r="A18" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="50"/>
     </row>
     <row r="19" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="49" t="s">
-        <v>238</v>
+      <c r="B19" s="51" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="49" t="s">
-        <v>239</v>
+      <c r="B20" s="51" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
-        <v>240</v>
-      </c>
-      <c r="B21" s="48"/>
+      <c r="A21" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="50"/>
     </row>
     <row r="22" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="49" t="s">
-        <v>241</v>
+      <c r="B22" s="51" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="B23" s="48"/>
+      <c r="A23" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="50"/>
     </row>
     <row r="24" ht="40" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="49" t="s">
-        <v>243</v>
+      <c r="B24" s="51" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
